--- a/data/trans_orig/P36B13-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B13-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121956</t>
+          <t>120936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162713</t>
+          <t>162824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86198</t>
+          <t>83927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121113</t>
+          <t>119145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>217699</t>
+          <t>217516</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>269871</t>
+          <t>272244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>114707</t>
+          <t>113762</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157174</t>
+          <t>154357</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106944</t>
+          <t>105977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143715</t>
+          <t>141891</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230900</t>
+          <t>231865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>285343</t>
+          <t>285040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105579</t>
+          <t>105158</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>144064</t>
+          <t>144243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>87721</t>
+          <t>85732</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120461</t>
+          <t>121470</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>200573</t>
+          <t>199469</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>253458</t>
+          <t>254401</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>15294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33569</t>
+          <t>34574</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22034</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26116</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49311</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82685</t>
+          <t>81457</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116549</t>
+          <t>116544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60602</t>
+          <t>60702</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93356</t>
+          <t>92477</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149430</t>
+          <t>153697</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198345</t>
+          <t>203293</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96943</t>
+          <t>97057</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134259</t>
+          <t>134128</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123894</t>
+          <t>124839</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162843</t>
+          <t>163051</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>231963</t>
+          <t>231116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286905</t>
+          <t>287726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106070</t>
+          <t>106758</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144821</t>
+          <t>144911</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>101492</t>
+          <t>101234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138374</t>
+          <t>140270</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>218913</t>
+          <t>216493</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>274479</t>
+          <t>272100</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>21685</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44239</t>
+          <t>44454</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18353</t>
+          <t>17577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36818</t>
+          <t>36973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43526</t>
+          <t>43601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74495</t>
+          <t>74305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>864</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9884</t>
+          <t>9720</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13054</t>
+          <t>13048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139222</t>
+          <t>135118</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180169</t>
+          <t>179248</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54936</t>
+          <t>52752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81457</t>
+          <t>79990</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>203168</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>251959</t>
+          <t>254037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121373</t>
+          <t>122176</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>162185</t>
+          <t>163746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35314</t>
+          <t>34657</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58127</t>
+          <t>60073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165013</t>
+          <t>164009</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>212316</t>
+          <t>212693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>141443</t>
+          <t>141958</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>185521</t>
+          <t>185502</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>27255</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>49233</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>172915</t>
+          <t>174815</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>222502</t>
+          <t>224770</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36711</t>
+          <t>36444</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63517</t>
+          <t>64174</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20432</t>
+          <t>20201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46566</t>
+          <t>46183</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75730</t>
+          <t>78494</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13648</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>304428</t>
+          <t>302919</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>366434</t>
+          <t>364047</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>207568</t>
+          <t>206786</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>256755</t>
+          <t>258021</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>523167</t>
+          <t>524509</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>605420</t>
+          <t>605437</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>325238</t>
+          <t>322523</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>387248</t>
+          <t>387015</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>216937</t>
+          <t>218285</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>271291</t>
+          <t>269002</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>558691</t>
+          <t>558148</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>638945</t>
+          <t>643885</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>286447</t>
+          <t>284261</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>348802</t>
+          <t>346977</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>228663</t>
+          <t>229317</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>280499</t>
+          <t>278305</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>528906</t>
+          <t>528153</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>613198</t>
+          <t>614265</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>106233</t>
+          <t>106779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>148650</t>
+          <t>149789</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63889</t>
+          <t>65683</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>99071</t>
+          <t>100562</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>181317</t>
+          <t>181590</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>235167</t>
+          <t>235898</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>19288</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17085</t>
+          <t>17543</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>38181</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>166702</t>
+          <t>165764</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>213776</t>
+          <t>213206</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>236644</t>
+          <t>236900</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>287026</t>
+          <t>289663</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>421755</t>
+          <t>421277</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>488970</t>
+          <t>490653</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>153180</t>
+          <t>152802</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>198502</t>
+          <t>198756</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>201830</t>
+          <t>202371</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>252050</t>
+          <t>252467</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>365572</t>
+          <t>367672</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>433334</t>
+          <t>432532</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>137669</t>
+          <t>136859</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>182361</t>
+          <t>181155</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>169882</t>
+          <t>168473</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>217872</t>
+          <t>214481</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>317937</t>
+          <t>320530</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>385058</t>
+          <t>385987</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>65578</t>
+          <t>64268</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>98610</t>
+          <t>99332</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>39194</t>
+          <t>39304</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>67965</t>
+          <t>68618</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>111322</t>
+          <t>111238</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>154067</t>
+          <t>155124</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20635</t>
+          <t>20692</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22972</t>
+          <t>23563</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18098</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>39321</t>
+          <t>39956</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>428183</t>
+          <t>425449</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>497017</t>
+          <t>493742</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>453658</t>
+          <t>454253</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>528858</t>
+          <t>526609</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>56650</t>
+          <t>57326</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>86874</t>
+          <t>86764</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>267472</t>
+          <t>269586</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>331814</t>
+          <t>331450</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>335295</t>
+          <t>337746</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>404985</t>
+          <t>404825</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>105565</t>
+          <t>105900</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>139185</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>208732</t>
+          <t>213550</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>266926</t>
+          <t>270775</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>326956</t>
+          <t>329667</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>391074</t>
+          <t>394647</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>47165</t>
+          <t>46273</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>74823</t>
+          <t>75479</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>49665</t>
+          <t>48465</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>80560</t>
+          <t>81083</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>103486</t>
+          <t>105419</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>146450</t>
+          <t>148323</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>19408</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>900565</t>
+          <t>891698</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1007779</t>
+          <t>1007224</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1146651</t>
+          <t>1144818</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1263403</t>
+          <t>1263686</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2072326</t>
+          <t>2069187</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2232834</t>
+          <t>2227904</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>938251</t>
+          <t>934428</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1043573</t>
+          <t>1046057</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1030044</t>
+          <t>1029041</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1141204</t>
+          <t>1138692</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1991449</t>
+          <t>1996119</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2151856</t>
+          <t>2152296</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>953476</t>
+          <t>953999</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1062503</t>
+          <t>1065182</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>897022</t>
+          <t>892570</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1003739</t>
+          <t>998764</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1872163</t>
+          <t>1884982</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2025382</t>
+          <t>2035947</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>338676</t>
+          <t>338502</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>407406</t>
+          <t>414891</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>222252</t>
+          <t>220341</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>280609</t>
+          <t>280502</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>578695</t>
+          <t>575358</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>671579</t>
+          <t>671748</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>34208</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>62828</t>
+          <t>61226</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>17042</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>37713</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>57036</t>
+          <t>55429</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>90891</t>
+          <t>89267</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -5734,32 +5734,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>170483</t>
+          <t>187577</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>150936</t>
+          <t>164888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>194527</t>
+          <t>211795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5769,32 +5769,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>154100</t>
+          <t>167590</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137718</t>
+          <t>149062</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171076</t>
+          <t>183064</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5804,32 +5804,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>324583</t>
+          <t>355167</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>297985</t>
+          <t>325236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>351291</t>
+          <t>382928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -5847,32 +5847,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>216100</t>
+          <t>227585</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>192221</t>
+          <t>204236</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239108</t>
+          <t>251602</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5882,32 +5882,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>203722</t>
+          <t>223930</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185159</t>
+          <t>205654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>222291</t>
+          <t>244609</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5917,32 +5917,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>419822</t>
+          <t>451515</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>391930</t>
+          <t>420463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>449209</t>
+          <t>483382</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -5960,32 +5960,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>94075</t>
+          <t>106959</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76911</t>
+          <t>87988</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114113</t>
+          <t>128615</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5995,32 +5995,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76881</t>
+          <t>83353</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62843</t>
+          <t>69286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>94506</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6030,32 +6030,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>170956</t>
+          <t>190312</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>151129</t>
+          <t>167335</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>195467</t>
+          <t>219204</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -6073,32 +6073,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33419</t>
+          <t>37302</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6108,32 +6108,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30882</t>
+          <t>34528</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21928</t>
+          <t>24226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43847</t>
+          <t>49505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -6186,17 +6186,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6221,32 +6221,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6256,22 +6256,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -6299,17 +6299,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6334,17 +6334,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>445913</t>
+          <t>486836</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>445913</t>
+          <t>486836</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>445913</t>
+          <t>486836</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6369,17 +6369,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>951126</t>
+          <t>1037455</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>951126</t>
+          <t>1037455</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>951126</t>
+          <t>1037455</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6416,32 +6416,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>116190</t>
+          <t>123010</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98432</t>
+          <t>105074</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133874</t>
+          <t>141832</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6451,32 +6451,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>115283</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102567</t>
+          <t>114065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129682</t>
+          <t>145364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6486,32 +6486,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>231473</t>
+          <t>252580</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206952</t>
+          <t>228123</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253597</t>
+          <t>276467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -6529,32 +6529,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>206931</t>
+          <t>222492</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>184091</t>
+          <t>200164</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>230848</t>
+          <t>244797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6564,32 +6564,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>169602</t>
+          <t>187115</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153418</t>
+          <t>169967</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185766</t>
+          <t>205454</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6599,32 +6599,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>376533</t>
+          <t>409607</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>347636</t>
+          <t>382007</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>405389</t>
+          <t>436461</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,25%</t>
         </is>
       </c>
     </row>
@@ -6642,32 +6642,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>103864</t>
+          <t>110734</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>94126</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122781</t>
+          <t>132687</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6677,32 +6677,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76776</t>
+          <t>84332</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63537</t>
+          <t>68987</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90862</t>
+          <t>100155</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6712,32 +6712,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>180639</t>
+          <t>195066</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>157532</t>
+          <t>172356</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>203244</t>
+          <t>220861</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -6755,22 +6755,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21958</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12896</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>39592</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6790,32 +6790,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30477</t>
+          <t>30750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41172</t>
+          <t>44043</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29091</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>62863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -6868,32 +6868,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6938,32 +6938,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -6981,17 +6981,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>380875</t>
+          <t>421380</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>380875</t>
+          <t>421380</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>380875</t>
+          <t>421380</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7051,17 +7051,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>833087</t>
+          <t>904592</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>833087</t>
+          <t>904592</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>833087</t>
+          <t>904592</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7098,32 +7098,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>107287</t>
+          <t>115489</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44432</t>
+          <t>97359</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>176884</t>
+          <t>134422</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7133,32 +7133,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>67199</t>
+          <t>75647</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57694</t>
+          <t>64867</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77429</t>
+          <t>87773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7168,32 +7168,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>174486</t>
+          <t>191136</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84131</t>
+          <t>170842</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>255528</t>
+          <t>215329</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -7211,32 +7211,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>172488</t>
+          <t>195988</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71332</t>
+          <t>176827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>283395</t>
+          <t>219149</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7246,32 +7246,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66941</t>
+          <t>74311</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57897</t>
+          <t>63204</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77539</t>
+          <t>86178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7281,32 +7281,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>239429</t>
+          <t>270300</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120713</t>
+          <t>245390</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>348559</t>
+          <t>295208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -7324,32 +7324,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>113952</t>
+          <t>123667</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43594</t>
+          <t>102465</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>191317</t>
+          <t>143476</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7359,32 +7359,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28862</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20847</t>
+          <t>24707</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37887</t>
+          <t>44437</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7394,32 +7394,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>142813</t>
+          <t>156862</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68020</t>
+          <t>135057</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>206578</t>
+          <t>179985</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -7437,32 +7437,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21258</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>41368</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7472,32 +7472,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>7790</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7507,32 +7507,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>24446</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>19856</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>46508</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -7550,32 +7550,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>250564</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>498739</t>
+          <t>14437</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>806</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7620,32 +7620,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>251286</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533298</t>
+          <t>15030</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -7663,17 +7663,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>665549</t>
+          <t>468947</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>665549</t>
+          <t>468947</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>665549</t>
+          <t>468947</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7698,17 +7698,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7733,17 +7733,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>832460</t>
+          <t>656444</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>832460</t>
+          <t>656444</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>832460</t>
+          <t>656444</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7780,32 +7780,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>292008</t>
+          <t>315076</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>262619</t>
+          <t>284318</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>323695</t>
+          <t>344107</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7815,32 +7815,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>433714</t>
+          <t>259748</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>283917</t>
+          <t>237106</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>702973</t>
+          <t>282890</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7850,32 +7850,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>725722</t>
+          <t>574824</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>567134</t>
+          <t>537063</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1101053</t>
+          <t>612495</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -7893,32 +7893,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>378260</t>
+          <t>407157</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>345382</t>
+          <t>374749</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>414013</t>
+          <t>442889</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7928,32 +7928,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>323793</t>
+          <t>351961</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>161661</t>
+          <t>327932</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>416033</t>
+          <t>379165</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7963,32 +7963,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>702053</t>
+          <t>759118</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>487808</t>
+          <t>722364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>797505</t>
+          <t>806839</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,54%</t>
         </is>
       </c>
     </row>
@@ -8006,32 +8006,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>273591</t>
+          <t>310144</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>241867</t>
+          <t>275730</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>302944</t>
+          <t>346503</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8041,32 +8041,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>183296</t>
+          <t>208554</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>91143</t>
+          <t>187017</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>241913</t>
+          <t>233069</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8076,32 +8076,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>456887</t>
+          <t>518698</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>313683</t>
+          <t>478186</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>523091</t>
+          <t>562072</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -8119,32 +8119,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>80617</t>
+          <t>87703</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61955</t>
+          <t>68660</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104784</t>
+          <t>112185</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8154,32 +8154,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>32574</t>
+          <t>36117</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>25972</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47428</t>
+          <t>50311</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8189,32 +8189,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>113191</t>
+          <t>123820</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78173</t>
+          <t>102008</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143263</t>
+          <t>152833</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -8232,32 +8232,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>11763</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20092</t>
+          <t>23451</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8267,32 +8267,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8302,32 +8302,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>13882</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24458</t>
+          <t>25493</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -8345,17 +8345,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8380,17 +8380,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>975435</t>
+          <t>858498</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>975435</t>
+          <t>858498</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>975435</t>
+          <t>858498</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8415,17 +8415,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2010253</t>
+          <t>1990341</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2010253</t>
+          <t>1990341</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2010253</t>
+          <t>1990341</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8462,32 +8462,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>112806</t>
+          <t>137860</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>96003</t>
+          <t>118330</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132090</t>
+          <t>159041</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8497,32 +8497,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>273226</t>
+          <t>305578</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>199175</t>
+          <t>284288</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>311672</t>
+          <t>327924</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8532,32 +8532,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>386032</t>
+          <t>443438</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>313604</t>
+          <t>414259</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>425426</t>
+          <t>476190</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -8575,32 +8575,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>190509</t>
+          <t>220826</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>168602</t>
+          <t>195877</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>214974</t>
+          <t>245224</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8610,32 +8610,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>255529</t>
+          <t>292465</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>195071</t>
+          <t>268471</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>292692</t>
+          <t>316060</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8645,32 +8645,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>446039</t>
+          <t>513291</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>364840</t>
+          <t>481813</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>494114</t>
+          <t>550280</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -8688,32 +8688,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>138283</t>
+          <t>168427</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>117022</t>
+          <t>143064</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>162563</t>
+          <t>195960</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8723,32 +8723,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>289148</t>
+          <t>205206</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>214931</t>
+          <t>184160</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>423622</t>
+          <t>228129</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8758,32 +8758,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>427431</t>
+          <t>373633</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>352883</t>
+          <t>341836</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>588036</t>
+          <t>410376</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -8801,32 +8801,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>34906</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>24237</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40076</t>
+          <t>50234</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8836,32 +8836,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>19641</t>
+          <t>23663</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>15725</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29487</t>
+          <t>32973</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8871,32 +8871,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>47459</t>
+          <t>58569</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>44320</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>64645</t>
+          <t>74450</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -8914,32 +8914,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8949,22 +8949,22 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8984,17 +8984,17 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>16163</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -9027,17 +9027,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>473614</t>
+          <t>566547</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>473614</t>
+          <t>566547</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>473614</t>
+          <t>566547</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9062,17 +9062,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>840147</t>
+          <t>829656</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>840147</t>
+          <t>829656</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>840147</t>
+          <t>829656</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9097,17 +9097,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1313761</t>
+          <t>1396203</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1313761</t>
+          <t>1396203</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1313761</t>
+          <t>1396203</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9144,32 +9144,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>39955</t>
+          <t>39986</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9179,32 +9179,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>284829</t>
+          <t>312301</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>261722</t>
+          <t>286597</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>308867</t>
+          <t>337310</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9214,32 +9214,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>306049</t>
+          <t>334962</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>274700</t>
+          <t>304998</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>335808</t>
+          <t>366125</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -9257,32 +9257,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>72599</t>
+          <t>65163</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>49561</t>
+          <t>45012</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>87223</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9292,32 +9292,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>265691</t>
+          <t>293079</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>240478</t>
+          <t>266321</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>291550</t>
+          <t>321706</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9327,32 +9327,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>338290</t>
+          <t>358241</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>305457</t>
+          <t>325196</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>373218</t>
+          <t>391140</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -9370,32 +9370,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>121971</t>
+          <t>121633</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>96416</t>
+          <t>96551</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>146288</t>
+          <t>147220</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9405,32 +9405,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>176060</t>
+          <t>198876</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>153979</t>
+          <t>172590</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>203918</t>
+          <t>228938</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9440,32 +9440,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>298031</t>
+          <t>320510</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>262817</t>
+          <t>283670</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>337484</t>
+          <t>357553</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -9483,32 +9483,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>39898</t>
+          <t>42813</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9518,32 +9518,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>35893</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>20851</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>46137</t>
+          <t>51336</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>52340</t>
+          <t>60055</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>37238</t>
+          <t>42766</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>74831</t>
+          <t>81343</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9666,32 +9666,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -9709,17 +9709,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9744,17 +9744,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>759236</t>
+          <t>842225</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>759236</t>
+          <t>842225</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>759236</t>
+          <t>842225</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9779,17 +9779,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>999743</t>
+          <t>1079453</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>999743</t>
+          <t>1079453</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>999743</t>
+          <t>1079453</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9826,32 +9826,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>819995</t>
+          <t>901673</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>592172</t>
+          <t>849471</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>902083</t>
+          <t>954216</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9861,32 +9861,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1328350</t>
+          <t>1250434</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1167189</t>
+          <t>1203099</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1761450</t>
+          <t>1301745</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9896,32 +9896,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2148345</t>
+          <t>2152106</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1920289</t>
+          <t>2079870</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2622965</t>
+          <t>2229127</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -9939,32 +9939,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1236887</t>
+          <t>1339209</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>908189</t>
+          <t>1278396</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1359152</t>
+          <t>1407859</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9974,67 +9974,67 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1285279</t>
+          <t>1422862</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1045384</t>
+          <t>1368377</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1395295</t>
+          <t>1480567</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
+          <t>40,83%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>3305</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2762071</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2679055</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>2848819</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
           <t>39,1%</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>3305</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>2522167</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>2212781</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>2709446</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>36,34%</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -10052,32 +10052,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>845736</t>
+          <t>941565</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>627479</t>
+          <t>878724</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>941266</t>
+          <t>1001448</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10087,32 +10087,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>831022</t>
+          <t>813517</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>696598</t>
+          <t>768687</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>994536</t>
+          <t>860069</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10122,32 +10122,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1676757</t>
+          <t>1755081</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1456955</t>
+          <t>1678472</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1866291</t>
+          <t>1840302</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -10165,32 +10165,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>194377</t>
+          <t>222147</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>147275</t>
+          <t>186375</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>234999</t>
+          <t>257600</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10200,32 +10200,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>115114</t>
+          <t>129056</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>90725</t>
+          <t>108726</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>140924</t>
+          <t>153868</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10235,32 +10235,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>309491</t>
+          <t>351203</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>254361</t>
+          <t>310114</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>354337</t>
+          <t>393759</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -10278,32 +10278,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>274919</t>
+          <t>33800</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>28832</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1170190</t>
+          <t>51329</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10313,32 +10313,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>18823</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>283672</t>
+          <t>44025</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>36278</t>
+          <t>31287</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1125327</t>
+          <t>59508</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -10391,17 +10391,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3371914</t>
+          <t>3438394</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3371914</t>
+          <t>3438394</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3371914</t>
+          <t>3438394</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10426,17 +10426,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3568517</t>
+          <t>3626093</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3568517</t>
+          <t>3626093</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3568517</t>
+          <t>3626093</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10461,17 +10461,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6940431</t>
+          <t>7064487</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6940431</t>
+          <t>7064487</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6940431</t>
+          <t>7064487</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
